--- a/app/database/MRA11/mroy_MRA1_04_motor_options.xlsx
+++ b/app/database/MRA11/mroy_MRA1_04_motor_options.xlsx
@@ -477,7 +477,7 @@
   <dimension ref="A1:M1048576"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.45"/>
@@ -487,7 +487,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="14.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="34.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="14" style="1" width="10.16"/>
   </cols>
@@ -561,10 +561,12 @@
       <c r="I2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4" t="b">
+      <c r="J2" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="L2" s="1" t="n">
@@ -602,10 +604,12 @@
       <c r="I3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4" t="b">
+      <c r="J3" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="L3" s="1" t="n">
@@ -643,10 +647,12 @@
       <c r="I4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4" t="b">
+      <c r="J4" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="L4" s="1" t="n">
@@ -684,10 +690,12 @@
       <c r="I5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="b">
+      <c r="J5" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="L5" s="1" t="n">
@@ -725,10 +733,12 @@
       <c r="I6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="4" t="b">
+      <c r="J6" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="L6" s="1" t="n">
@@ -766,10 +776,12 @@
       <c r="I7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" s="4" t="b">
+      <c r="J7" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="L7" s="1" t="n">
@@ -807,10 +819,12 @@
       <c r="I8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="4" t="b">
+      <c r="J8" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="L8" s="1" t="n">
@@ -848,10 +862,12 @@
       <c r="I9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="4" t="b">
+      <c r="J9" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="L9" s="1" t="n">
@@ -889,10 +905,12 @@
       <c r="I10" s="1" t="n">
         <v>4112000010</v>
       </c>
-      <c r="J10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" s="4" t="b">
+      <c r="J10" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="L10" s="1" t="n">
@@ -930,10 +948,12 @@
       <c r="I11" s="1" t="n">
         <v>4112000310</v>
       </c>
-      <c r="J11" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4" t="b">
+      <c r="J11" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="L11" s="1" t="n">
@@ -971,10 +991,12 @@
       <c r="I12" s="1" t="n">
         <v>4112002320</v>
       </c>
-      <c r="J12" s="4" t="b">
+      <c r="J12" s="4" t="n">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K12" s="4" t="b">
+      <c r="K12" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="L12" s="1" t="n">
@@ -1012,10 +1034,12 @@
       <c r="I13" s="1" t="n">
         <v>4112002030</v>
       </c>
-      <c r="J13" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" s="4" t="b">
+      <c r="J13" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="L13" s="1" t="n">
@@ -1053,10 +1077,12 @@
       <c r="I14" s="1" t="n">
         <v>4112002340</v>
       </c>
-      <c r="J14" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" s="4" t="b">
+      <c r="J14" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="L14" s="1" t="n">
@@ -1094,10 +1120,12 @@
       <c r="I15" s="1" t="n">
         <v>4112004310</v>
       </c>
-      <c r="J15" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" s="4" t="b">
+      <c r="J15" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="L15" s="1" t="n">
@@ -1135,10 +1163,12 @@
       <c r="I16" s="1" t="n">
         <v>4112004320</v>
       </c>
-      <c r="J16" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" s="4" t="b">
+      <c r="J16" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="L16" s="1" t="n">
@@ -1176,10 +1206,12 @@
       <c r="I17" s="1" t="n">
         <v>4112004330</v>
       </c>
-      <c r="J17" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" s="4" t="b">
+      <c r="J17" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="L17" s="1" t="n">
